--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T11:00:33+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T11:53:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:53:44+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T12:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T12:55:48+01:00</t>
+    <t>2026-03-18T17:09:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$167</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6786" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6230" uniqueCount="780">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T11:10:04+02:00</t>
+    <t>2026-06-24T16:51:19+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2043,8 +2043,12 @@
     <t>To represent information about how the services are to be delivered use the `instructions` element.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:reference}
+    <t xml:space="preserve">value:identifier.type.coding.code}
 </t>
+  </si>
+  <si>
+    <t>befund_Medikation
+ausnahmeindikation</t>
   </si>
   <si>
     <t>Request.supportingInfo</t>
@@ -2319,54 +2323,6 @@
   </si>
   <si>
     <t>Dieses Element wird zur Angabe von Ausnahmekennziffern genutzt z.B. technische Kennziffer.</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen</t>
-  </si>
-  <si>
-    <t>ZusaetzlicheInformationen</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.reference</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.type</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.identifier</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.identifier.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.identifier.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.identifier.use</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.identifier.type</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.identifier.system</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.identifier.value</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.identifier.period</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.identifier.assigner</t>
-  </si>
-  <si>
-    <t>ServiceRequest.supportingInfo:ZusaetzlicheInformationen.display</t>
   </si>
   <si>
     <t>ServiceRequest.specimen</t>
@@ -2794,12 +2750,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO182"/>
+  <dimension ref="A1:AO167"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="71.19140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="54.125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.3828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="38.546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -2824,7 +2780,7 @@
     <col min="25" max="25" width="162.58984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="59.92578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="28.01953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
@@ -10350,7 +10306,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>89</v>
@@ -11048,7 +11004,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>89</v>
@@ -15671,12 +15627,14 @@
       <c r="AB110" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="AC110" s="2"/>
+      <c r="AC110" t="s" s="2">
+        <v>653</v>
+      </c>
       <c r="AD110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>646</v>
@@ -15694,13 +15652,13 @@
         <v>259</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
@@ -15711,13 +15669,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>646</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>647</v>
@@ -15739,7 +15697,7 @@
         <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>649</v>
@@ -15813,13 +15771,13 @@
         <v>259</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
@@ -15830,10 +15788,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15945,10 +15903,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16062,10 +16020,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16179,10 +16137,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16296,10 +16254,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16325,10 +16283,10 @@
         <v>231</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>447</v>
@@ -16413,10 +16371,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16528,10 +16486,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16645,10 +16603,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16764,10 +16722,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16883,10 +16841,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16998,10 +16956,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17115,10 +17073,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17234,10 +17192,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17349,10 +17307,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17466,10 +17424,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17511,7 +17469,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>81</v>
@@ -17585,10 +17543,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17702,10 +17660,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17747,7 +17705,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>81</v>
@@ -17821,10 +17779,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17940,10 +17898,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18059,10 +18017,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18178,10 +18136,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18297,10 +18255,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18414,10 +18372,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18531,10 +18489,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18648,10 +18606,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18677,10 +18635,10 @@
         <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>453</v>
@@ -18765,13 +18723,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>646</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>647</v>
@@ -18867,13 +18825,13 @@
         <v>259</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -18884,10 +18842,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18999,10 +18957,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19116,10 +19074,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19233,10 +19191,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19350,10 +19308,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19379,10 +19337,10 @@
         <v>231</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>447</v>
@@ -19467,10 +19425,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19582,10 +19540,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19699,10 +19657,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19818,10 +19776,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19937,10 +19895,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20052,10 +20010,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20169,10 +20127,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20288,10 +20246,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20403,10 +20361,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20520,10 +20478,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20565,7 +20523,7 @@
       </c>
       <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="S152" t="s" s="2">
         <v>81</v>
@@ -20639,10 +20597,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20756,10 +20714,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20801,7 +20759,7 @@
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>81</v>
@@ -20875,10 +20833,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20994,10 +20952,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21113,10 +21071,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21232,10 +21190,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21351,10 +21309,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21468,10 +21426,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21585,10 +21543,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21702,10 +21660,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21731,10 +21689,10 @@
         <v>105</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>453</v>
@@ -21817,46 +21775,44 @@
         <v>81</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C163" t="s" s="2">
         <v>745</v>
       </c>
+      <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>647</v>
+        <v>81</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J163" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J163" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K163" t="s" s="2">
-        <v>648</v>
+        <v>746</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>649</v>
+        <v>747</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>650</v>
+        <v>748</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>651</v>
+        <v>749</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21906,7 +21862,7 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>646</v>
+        <v>745</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -21921,13 +21877,13 @@
         <v>259</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>653</v>
+        <v>81</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>654</v>
+        <v>750</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>655</v>
+        <v>751</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>81</v>
@@ -21938,21 +21894,21 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>660</v>
+        <v>752</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>81</v>
+        <v>753</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>81</v>
@@ -21961,19 +21917,23 @@
         <v>81</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>105</v>
+        <v>304</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>106</v>
+        <v>754</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>755</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>757</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
       </c>
@@ -21997,13 +21957,13 @@
         <v>81</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>81</v>
+        <v>758</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>81</v>
+        <v>759</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>81</v>
@@ -22021,53 +21981,53 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>108</v>
+        <v>752</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>81</v>
+        <v>750</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>109</v>
+        <v>760</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>81</v>
+        <v>761</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>662</v>
+        <v>762</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>81</v>
@@ -22079,16 +22039,16 @@
         <v>81</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>112</v>
+        <v>763</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>114</v>
+        <v>764</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>115</v>
+        <v>765</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22126,19 +22086,19 @@
         <v>81</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC165" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD165" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>119</v>
+        <v>762</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22150,30 +22110,30 @@
         <v>101</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>81</v>
+        <v>766</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>103</v>
+        <v>767</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>81</v>
+        <v>768</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>748</v>
+        <v>769</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>664</v>
+        <v>769</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22181,13 +22141,13 @@
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>81</v>
@@ -22199,13 +22159,13 @@
         <v>105</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>432</v>
+        <v>770</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>433</v>
+        <v>771</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>434</v>
+        <v>343</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22255,7 +22215,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>435</v>
+        <v>769</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22264,7 +22224,7 @@
         <v>89</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>436</v>
+        <v>101</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>102</v>
@@ -22273,10 +22233,10 @@
         <v>81</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>103</v>
+        <v>772</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>81</v>
@@ -22287,10 +22247,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>749</v>
+        <v>773</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>666</v>
+        <v>773</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22310,19 +22270,19 @@
         <v>81</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>133</v>
+        <v>774</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>438</v>
+        <v>775</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>439</v>
+        <v>776</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>440</v>
+        <v>777</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -22348,13 +22308,13 @@
         <v>81</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>81</v>
@@ -22372,1799 +22332,38 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>443</v>
+        <v>773</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>102</v>
+        <v>259</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>81</v>
+        <v>778</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>103</v>
+        <v>779</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="168" hidden="true">
-      <c r="A168" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="C168" s="2"/>
-      <c r="D168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E168" s="2"/>
-      <c r="F168" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G168" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J168" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K168" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L168" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O168" s="2"/>
-      <c r="P168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q168" s="2"/>
-      <c r="R168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AG168" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH168" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI168" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ168" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL168" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO168" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="169" hidden="true">
-      <c r="A169" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C169" s="2"/>
-      <c r="D169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E169" s="2"/>
-      <c r="F169" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G169" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K169" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L169" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N169" s="2"/>
-      <c r="O169" s="2"/>
-      <c r="P169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q169" s="2"/>
-      <c r="R169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF169" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG169" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH169" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM169" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="170" hidden="true">
-      <c r="A170" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="C170" s="2"/>
-      <c r="D170" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E170" s="2"/>
-      <c r="F170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G170" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K170" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L170" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O170" s="2"/>
-      <c r="P170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q170" s="2"/>
-      <c r="R170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF170" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH170" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI170" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ170" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM170" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AN170" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="171" hidden="true">
-      <c r="A171" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="C171" s="2"/>
-      <c r="D171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E171" s="2"/>
-      <c r="F171" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G171" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I171" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J171" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K171" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L171" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="P171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q171" s="2"/>
-      <c r="R171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X171" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="Z171" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AA171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF171" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AG171" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH171" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI171" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ171" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL171" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AM171" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AN171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO171" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="172" hidden="true">
-      <c r="A172" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="C172" s="2"/>
-      <c r="D172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E172" s="2"/>
-      <c r="F172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G172" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J172" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K172" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="L172" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="P172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q172" s="2"/>
-      <c r="R172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X172" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y172" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="Z172" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AA172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF172" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AG172" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH172" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI172" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ172" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AM172" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AN172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO172" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="173" hidden="true">
-      <c r="A173" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C173" s="2"/>
-      <c r="D173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E173" s="2"/>
-      <c r="F173" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G173" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J173" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K173" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L173" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="P173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q173" s="2"/>
-      <c r="R173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T173" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="U173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF173" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AG173" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH173" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI173" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ173" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL173" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AM173" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AN173" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO173" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="174" hidden="true">
-      <c r="A174" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="C174" s="2"/>
-      <c r="D174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E174" s="2"/>
-      <c r="F174" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G174" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J174" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K174" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L174" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O174" s="2"/>
-      <c r="P174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q174" s="2"/>
-      <c r="R174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T174" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="U174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF174" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AG174" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH174" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI174" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ174" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL174" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AM174" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AN174" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO174" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="175" hidden="true">
-      <c r="A175" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="C175" s="2"/>
-      <c r="D175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E175" s="2"/>
-      <c r="F175" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G175" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J175" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K175" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="L175" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O175" s="2"/>
-      <c r="P175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q175" s="2"/>
-      <c r="R175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF175" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG175" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH175" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI175" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ175" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AK175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL175" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AM175" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="176" hidden="true">
-      <c r="A176" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C176" s="2"/>
-      <c r="D176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E176" s="2"/>
-      <c r="F176" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G176" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J176" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K176" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="L176" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O176" s="2"/>
-      <c r="P176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q176" s="2"/>
-      <c r="R176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF176" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AG176" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH176" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI176" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ176" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AK176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL176" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AM176" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO176" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="177" hidden="true">
-      <c r="A177" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="C177" s="2"/>
-      <c r="D177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E177" s="2"/>
-      <c r="F177" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G177" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J177" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K177" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L177" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O177" s="2"/>
-      <c r="P177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q177" s="2"/>
-      <c r="R177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF177" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG177" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH177" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI177" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ177" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM177" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="178" hidden="true">
-      <c r="A178" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="C178" s="2"/>
-      <c r="D178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E178" s="2"/>
-      <c r="F178" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G178" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J178" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K178" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="O178" s="2"/>
-      <c r="P178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q178" s="2"/>
-      <c r="R178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="AG178" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH178" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI178" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ178" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AK178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL178" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="AM178" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="AN178" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO178" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="179" hidden="true">
-      <c r="A179" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="C179" s="2"/>
-      <c r="D179" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="E179" s="2"/>
-      <c r="F179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J179" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K179" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="P179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q179" s="2"/>
-      <c r="R179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X179" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="AG179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH179" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI179" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ179" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL179" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="AM179" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO179" t="s" s="2">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="180" hidden="true">
-      <c r="A180" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="C180" s="2"/>
-      <c r="D180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E180" s="2"/>
-      <c r="F180" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G180" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K180" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="O180" s="2"/>
-      <c r="P180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q180" s="2"/>
-      <c r="R180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="AG180" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH180" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI180" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ180" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK180" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="AL180" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="AN180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO180" t="s" s="2">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="181" hidden="true">
-      <c r="A181" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="C181" s="2"/>
-      <c r="D181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G181" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J181" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K181" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O181" s="2"/>
-      <c r="P181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q181" s="2"/>
-      <c r="R181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="AG181" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH181" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI181" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ181" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL181" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AM181" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="AN181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO181" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="182" hidden="true">
-      <c r="A182" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="C182" s="2"/>
-      <c r="D182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E182" s="2"/>
-      <c r="F182" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G182" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K182" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="L182" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="O182" s="2"/>
-      <c r="P182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q182" s="2"/>
-      <c r="R182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF182" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="AG182" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH182" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI182" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AJ182" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AK182" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="AL182" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AM182" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="AN182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO182" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO182">
+  <autoFilter ref="A1:AO167">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -24174,7 +22373,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI181">
+  <conditionalFormatting sqref="A2:AI166">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:51:19+02:00</t>
+    <t>2026-06-26T18:38:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T18:38:01+02:00</t>
+    <t>2026-07-06T17:54:18+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T17:54:18+02:00</t>
+    <t>2026-07-22T15:49:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-ServiceRequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:49:40+02:00</t>
+    <t>2026-07-22T16:29:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
